--- a/public/exports-from-60/44023911.xlsx
+++ b/public/exports-from-60/44023911.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218776</t>
+          <t xml:space="preserve">311218780</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289447</t>
+          <t xml:space="preserve">311289501</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289447</t>
+          <t xml:space="preserve">311289501</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289447</t>
+          <t xml:space="preserve">311289501</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289441</t>
+          <t xml:space="preserve">311289442</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M95" t="inlineStr">

--- a/public/exports-from-60/44023911.xlsx
+++ b/public/exports-from-60/44023911.xlsx
@@ -6889,7 +6889,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289501</t>
+          <t xml:space="preserve">311289447</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289501</t>
+          <t xml:space="preserve">311289447</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289501</t>
+          <t xml:space="preserve">311289447</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289442</t>
+          <t xml:space="preserve">311289441</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">

--- a/public/exports-from-60/44023911.xlsx
+++ b/public/exports-from-60/44023911.xlsx
@@ -5689,7 +5689,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218780</t>
+          <t xml:space="preserve">311218776</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
